--- a/lab-standards/WEAB-lab-standard.xlsx
+++ b/lab-standards/WEAB-lab-standard.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -138,6 +138,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -647,7 +653,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -671,7 +677,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -695,7 +701,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -719,7 +725,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -743,7 +749,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -767,7 +773,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -791,7 +797,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -815,7 +821,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -839,7 +845,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -863,7 +869,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -887,7 +893,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -911,7 +917,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -935,7 +941,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -959,7 +965,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -983,7 +989,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1007,7 +1013,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1031,7 +1037,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1055,7 +1061,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1079,7 +1085,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1103,7 +1109,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1111,18 +1117,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1131,7 +1137,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -1139,7 +1145,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1148,11 +1154,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1317,7 +1323,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1341,7 +1347,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1365,7 +1371,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1389,7 +1395,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1413,7 +1419,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1437,7 +1443,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1461,7 +1467,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1485,7 +1491,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1509,7 +1515,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -1533,7 +1539,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -1557,7 +1563,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -1581,7 +1587,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -1605,7 +1611,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -1629,7 +1635,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -1653,7 +1659,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1677,7 +1683,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1701,7 +1707,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1725,7 +1731,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1749,7 +1755,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1773,7 +1779,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -1797,7 +1803,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -1821,7 +1827,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -1845,7 +1851,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -1869,7 +1875,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1877,18 +1883,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="10">
+      <c r="E39" s="15">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="15">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1897,7 +1903,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="10">
+      <c r="F40" s="15">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -1905,7 +1911,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1914,11 +1920,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="10">
+      <c r="F42" s="15">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1945,7 +1951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -2004,10 +2010,6 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2018,15 +2020,11 @@
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Classroom – 350 sft (33 sqm)
-Workshop/ lab – 800 sft (75 sqm)
+lab size – 500 sft (47 sqm)
 OR
-Classroom cum workshop – 1000 sft (93 sqm)</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="12" t="n"/>
+Classroom cum workshop – 500 sft (47 sqm)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2085,7 +2083,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2109,7 +2107,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2133,7 +2131,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2157,7 +2155,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2181,7 +2179,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2205,12 +2203,13 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Tools: Office application, photo editing software and video editing software</t>
+          <t>Tools: 
+Office application, photo editing software and video editing software, SEO Tools, Social Media Management, Email Marketing, Content Creation, CRM, Data Entry, Affiliate Marketing, bid for job, ad campaigns</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
@@ -2229,7 +2228,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2253,12 +2252,12 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Internet connectivity with power back-up</t>
+          <t>Internet connectivity (Minimum 10 Mbps) with power back-up (at least 01 hour)</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
@@ -2277,7 +2276,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2285,18 +2284,18 @@
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="10">
+      <c r="E24" s="17">
         <f>SUM(E16:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="17">
         <f>SUM(F16:F23)</f>
         <v/>
       </c>
       <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2305,7 +2304,7 @@
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="12" t="n"/>
-      <c r="F25" s="10">
+      <c r="F25" s="17">
         <f>F24/E24*100</f>
         <v/>
       </c>
@@ -2313,7 +2312,7 @@
     </row>
     <row r="26" ht="9.75" customHeight="1"/>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2322,18 +2321,25 @@
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="10">
+      <c r="F27" s="17">
         <f>F25*30/100</f>
         <v/>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
     </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the lab should be air-conditioned. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
@@ -2342,6 +2348,7 @@
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2412,6 +2419,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2427,6 +2438,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3156,7 +3171,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3180,7 +3195,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3204,7 +3219,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3228,7 +3243,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3252,7 +3267,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3276,7 +3291,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3300,7 +3315,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3324,7 +3339,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -3348,7 +3363,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -3372,7 +3387,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -3396,7 +3411,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -3420,7 +3435,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -3444,7 +3459,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -3468,7 +3483,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -3492,7 +3507,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -3516,7 +3531,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3540,7 +3555,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3564,7 +3579,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3588,7 +3603,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3596,18 +3611,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="10">
+      <c r="E34" s="15">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="15">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3616,7 +3631,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -3624,7 +3639,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3633,11 +3648,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="10">
+      <c r="F37" s="15">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3723,10 +3738,6 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3736,13 +3747,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Classroom cum workshop – 500 - 600 sft (50-55 sqm)</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="12" t="n"/>
+          <t>Classroom – 350 sft (33 sqm)
+lab size – 500 sft (47 sqm)
+OR
+Classroom cum workshop – 500 sft (47 sqm)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3801,12 +3811,13 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Laptop/ Desktop (Minimum Intel core i5-i3 6 gen or AMD Ryzen 5), Ram: minimum 8 - 16 GB, Graphic Card: dedicated GPU 2GB, High Speed Internet (Minimum 10 Mbps), Graphic Design Software (Photoshop CC, Illustrator CC, CorelDraw)</t>
+          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
+(Photoshop CC, Illustrator CC, InDesign, After Effects, CorelDraw); 3D Design Software (Blender, Cinema 4D or Autodesk Maya)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -3825,7 +3836,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3849,7 +3860,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3873,7 +3884,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3897,7 +3908,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3921,7 +3932,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3945,7 +3956,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3969,16 +3980,16 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Air-conditioning (suited with workshop lab size)</t>
+          <t>Ergonomic chairs and desks (Plastic chairs/stool not acceptable)</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>0</v>
@@ -3992,96 +4003,80 @@
       </c>
       <c r="G23" s="9" t="n"/>
     </row>
-    <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Ergonomic chairs and desks (Plastic chairs/stool not acceptable)</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="9">
-        <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
-        <v/>
-      </c>
-      <c r="G24" s="9" t="n"/>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="17">
+        <f>SUM(E16:E23)</f>
+        <v/>
+      </c>
+      <c r="F24" s="17">
+        <f>SUM(F16:F23)</f>
+        <v/>
+      </c>
+      <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Sum</t>
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Score out of 100</t>
         </is>
       </c>
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="10">
-        <f>SUM(E16:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="10">
-        <f>SUM(F16:F24)</f>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="17">
+        <f>F24/E24*100</f>
         <v/>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Score out of 100</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="10">
-        <f>F25/E25*100</f>
-        <v/>
-      </c>
-      <c r="G26" s="13" t="n"/>
-    </row>
-    <row r="27" ht="9.75" customHeight="1"/>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="26" ht="9.75" customHeight="1"/>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10">
-        <f>F26*30/100</f>
-        <v/>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="17">
+        <f>F25*30/100</f>
+        <v/>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
     </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the lab should be air-conditioned. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A24:D24"/>
     <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4231,7 +4226,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -4255,7 +4250,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -4279,7 +4274,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -4303,7 +4298,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -4327,7 +4322,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -4351,7 +4346,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -4375,7 +4370,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4399,7 +4394,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -4423,7 +4418,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -4447,7 +4442,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -4471,7 +4466,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -4495,7 +4490,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -4519,7 +4514,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -4543,7 +4538,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -4567,7 +4562,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -4591,7 +4586,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -4615,7 +4610,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -4639,7 +4634,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -4663,7 +4658,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4687,7 +4682,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -4695,18 +4690,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -4715,7 +4710,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -4723,7 +4718,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -4732,11 +4727,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>

--- a/lab-standards/WEAB-lab-standard.xlsx
+++ b/lab-standards/WEAB-lab-standard.xlsx
@@ -653,7 +653,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -677,7 +677,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -701,7 +701,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -725,7 +725,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -749,7 +749,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -773,7 +773,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -797,7 +797,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -821,7 +821,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -845,7 +845,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -893,7 +893,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -917,7 +917,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -941,7 +941,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -965,7 +965,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -989,7 +989,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1013,7 +1013,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1061,7 +1061,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1109,7 +1109,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1117,18 +1117,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="15">
+      <c r="E35" s="17">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1137,7 +1137,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="15">
+      <c r="F36" s="17">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1154,11 +1154,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="15">
+      <c r="F38" s="17">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1323,7 +1323,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1347,7 +1347,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1371,7 +1371,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1395,7 +1395,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1419,7 +1419,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1443,7 +1443,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1491,7 +1491,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1515,7 +1515,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -1539,7 +1539,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -1563,7 +1563,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -1587,7 +1587,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -1611,7 +1611,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -1635,7 +1635,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -1659,7 +1659,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1683,7 +1683,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1707,7 +1707,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1731,7 +1731,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1755,7 +1755,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1779,7 +1779,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="14" t="n">
+      <c r="A35" s="16" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -1803,7 +1803,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="14" t="n">
+      <c r="A36" s="16" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -1827,7 +1827,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="14" t="n">
+      <c r="A37" s="16" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -1851,7 +1851,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="16" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -1875,7 +1875,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1883,18 +1883,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="15">
+      <c r="E39" s="17">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="17">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1903,7 +1903,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="15">
+      <c r="F40" s="17">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -1911,7 +1911,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1920,11 +1920,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="15">
+      <c r="F42" s="17">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="15" t="inlineStr">
+      <c r="G42" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1970,6 +1970,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1992,6 +1993,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -2010,6 +2012,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2025,7 +2031,13 @@
 Classroom cum workshop – 500 sft (47 sqm)</t>
         </is>
       </c>
-    </row>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -2033,6 +2045,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -2044,6 +2057,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -2160,7 +2174,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Computers/Laptop: (Minimum Intel Core i5 processor (8th Gen), 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
+          <t>Computers/Laptop: (Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
@@ -2500,7 +2514,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2524,7 +2538,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2548,7 +2562,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2572,7 +2586,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2596,7 +2610,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2620,7 +2634,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2644,7 +2658,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2668,7 +2682,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2692,7 +2706,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2716,7 +2730,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2740,7 +2754,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2764,7 +2778,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2788,7 +2802,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2812,7 +2826,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2836,7 +2850,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -2860,7 +2874,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -2884,7 +2898,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -2908,7 +2922,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2932,7 +2946,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -2956,7 +2970,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2964,18 +2978,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="15">
+      <c r="E35" s="17">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2984,7 +2998,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="15">
+      <c r="F36" s="17">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -2992,7 +3006,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3001,11 +3015,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="15">
+      <c r="F38" s="17">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3171,7 +3185,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3195,7 +3209,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3219,7 +3233,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3243,7 +3257,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3267,7 +3281,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3291,7 +3305,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3315,7 +3329,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3339,7 +3353,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -3363,7 +3377,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -3387,7 +3401,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -3411,7 +3425,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -3435,7 +3449,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -3459,7 +3473,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -3483,7 +3497,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -3507,7 +3521,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -3531,7 +3545,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3555,7 +3569,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3579,7 +3593,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3603,7 +3617,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3611,18 +3625,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="15">
+      <c r="E34" s="17">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="17">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3631,7 +3645,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -3639,7 +3653,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3648,11 +3662,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="15">
+      <c r="F37" s="17">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="15" t="inlineStr">
+      <c r="G37" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3738,6 +3752,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3753,6 +3771,10 @@
 Classroom cum workshop – 500 sft (47 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4226,7 +4248,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -4250,7 +4272,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -4274,7 +4296,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -4298,7 +4320,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -4322,7 +4344,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -4346,7 +4368,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -4370,7 +4392,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4394,7 +4416,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -4418,7 +4440,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -4442,7 +4464,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -4466,7 +4488,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -4490,7 +4512,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -4514,7 +4536,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -4538,7 +4560,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -4562,7 +4584,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -4586,7 +4608,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -4610,7 +4632,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -4634,7 +4656,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -4658,7 +4680,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4682,7 +4704,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -4690,18 +4712,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="15">
+      <c r="E35" s="17">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -4710,7 +4732,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="15">
+      <c r="F36" s="17">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -4718,7 +4740,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -4727,11 +4749,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="15">
+      <c r="F38" s="17">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>

--- a/lab-standards/WEAB-lab-standard.xlsx
+++ b/lab-standards/WEAB-lab-standard.xlsx
@@ -1970,7 +1970,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1993,7 +1992,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -2036,8 +2034,6 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -2045,7 +2041,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -2057,7 +2052,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -3712,6 +3706,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3734,6 +3729,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -3776,6 +3772,8 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -3783,6 +3781,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -3794,6 +3793,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
+          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 8 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
 (Photoshop CC, Illustrator CC, InDesign, After Effects, CorelDraw); 3D Design Software (Blender, Cinema 4D or Autodesk Maya)</t>
         </is>
       </c>

--- a/lab-standards/WEAB-lab-standard.xlsx
+++ b/lab-standards/WEAB-lab-standard.xlsx
@@ -1970,6 +1970,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1992,6 +1993,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -2034,6 +2036,8 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -2041,6 +2045,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="115.65" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -2052,6 +2057,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="26.85" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -2168,7 +2174,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Computers/Laptop: (Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
+          <t>Computers/Laptop: (Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (19/20-inch minimum, with color accuracy).</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
@@ -3838,7 +3844,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 8 gen/above, or AMD Ryzen 5/ similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
+          <t>Laptop/ Desktop (Minimum Intel core i5 or Intel core i3 8 gen/above, or AMD Ryzen similar spec; Ram: minimum 8 - 16 GB; Display: FHD monitor; Graphic Card: dedicated GPU 2GB; High Speed Internet (Minimum 10 Mbps); Graphic Design Software 
 (Photoshop CC, Illustrator CC, InDesign, After Effects, CorelDraw); 3D Design Software (Blender, Cinema 4D or Autodesk Maya)</t>
         </is>
       </c>
